--- a/files/availability-list-september-2026.xlsx
+++ b/files/availability-list-september-2026.xlsx
@@ -529,7 +529,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Spring / Summer 2026 Availability · Generated 8 September 2026 · papervaletrees.com · 028 3085 0059</t>
+          <t>Generated 12 September 2026 · papervaletrees.com · 028 3085 0059</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I135" s="4" t="inlineStr"/>
     </row>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I140" s="4" t="inlineStr"/>
     </row>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I146" s="4" t="inlineStr"/>
     </row>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I148" s="4" t="inlineStr"/>
     </row>
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
     </row>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I187" s="4" t="inlineStr"/>
     </row>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I199" s="4" t="inlineStr"/>
     </row>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I229" s="4" t="inlineStr"/>
     </row>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="H230" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I230" s="4" t="inlineStr"/>
     </row>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="H240" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I240" s="4" t="inlineStr"/>
     </row>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="H284" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I284" s="4" t="inlineStr"/>
     </row>
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="H366" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I366" s="4" t="inlineStr"/>
     </row>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="H380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I380" s="4" t="inlineStr"/>
     </row>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="H442" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I442" s="4" t="inlineStr"/>
     </row>
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I518" s="4" t="inlineStr"/>
     </row>
@@ -21682,7 +21682,7 @@
         </is>
       </c>
       <c r="H553" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I553" s="4" t="inlineStr"/>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I570" s="4" t="inlineStr"/>
     </row>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="H615" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I615" s="4" t="inlineStr"/>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="H616" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I616" s="4" t="inlineStr"/>
     </row>
@@ -24335,7 +24335,7 @@
         </is>
       </c>
       <c r="H622" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I622" s="4" t="inlineStr"/>
     </row>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="H634" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I634" s="4" t="inlineStr"/>
     </row>
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="H647" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I647" s="4" t="inlineStr"/>
     </row>
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="H652" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I652" s="4" t="inlineStr"/>
     </row>
@@ -25662,7 +25662,7 @@
         </is>
       </c>
       <c r="H657" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I657" s="4" t="inlineStr"/>
     </row>
@@ -25699,7 +25699,7 @@
         </is>
       </c>
       <c r="H658" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I658" s="4" t="inlineStr"/>
     </row>
@@ -26044,7 +26044,7 @@
         </is>
       </c>
       <c r="H667" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I667" s="4" t="inlineStr"/>
     </row>
@@ -27256,7 +27256,7 @@
         </is>
       </c>
       <c r="H699" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I699" s="4" t="inlineStr"/>
     </row>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="H702" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="I702" s="4" t="inlineStr"/>
     </row>
@@ -27847,7 +27847,7 @@
         </is>
       </c>
       <c r="H714" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I714" s="4" t="inlineStr"/>
     </row>
@@ -28044,7 +28044,7 @@
         </is>
       </c>
       <c r="H719" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I719" s="4" t="inlineStr"/>
     </row>

--- a/files/availability-list-september-2026.xlsx
+++ b/files/availability-list-september-2026.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I823"/>
+  <dimension ref="A1:I822"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 22 September 2026 · papervaletrees.com · 028 3085 0059</t>
+          <t>Generated 27 September 2026 · papervaletrees.com · 028 3085 0059</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
     </row>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I203" s="4" t="inlineStr"/>
     </row>
@@ -14208,7 +14208,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I351" s="4" t="inlineStr"/>
     </row>
@@ -16640,7 +16640,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I415" s="4" t="inlineStr"/>
     </row>
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="H436" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I436" s="4" t="inlineStr"/>
     </row>
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="H439" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I439" s="4" t="inlineStr"/>
     </row>
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="H440" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I440" s="4" t="inlineStr"/>
     </row>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="H460" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I460" s="4" t="inlineStr"/>
     </row>
@@ -18464,7 +18464,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I463" s="4" t="inlineStr"/>
     </row>
@@ -20304,7 +20304,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I511" s="4" t="inlineStr"/>
     </row>
@@ -20600,7 +20600,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I519" s="4" t="inlineStr"/>
     </row>
@@ -20822,7 +20822,7 @@
         </is>
       </c>
       <c r="H525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I525" s="4" t="inlineStr"/>
     </row>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="H535" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I535" s="4" t="inlineStr"/>
     </row>
@@ -24416,7 +24416,7 @@
         </is>
       </c>
       <c r="H619" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I619" s="4" t="inlineStr"/>
     </row>
@@ -25876,85 +25876,85 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>PYRUS domestica 'Doyenne du Comice'</t>
+          <t>PYRUS salicifolia ‘Pendula’</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Comice Pear</t>
+          <t>Weeping Silver Pear</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F657" t="inlineStr"/>
+          <t>200-250cm</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£80.00</t>
         </is>
       </c>
       <c r="H657" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I657" s="4" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>PYRUS salicifolia ‘Pendula’</t>
+          <t>QUERCUS acutissima</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Weeping Silver Pear</t>
+          <t>Sawtooth Oak</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F658" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr"/>
       <c r="G658" t="inlineStr">
         <is>
-          <t>£80.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H658" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I658" s="4" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -25969,29 +25969,33 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F659" t="inlineStr"/>
+          <t>350-400 cm</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£195.00</t>
         </is>
       </c>
       <c r="H659" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I659" s="4" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -26006,33 +26010,33 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>350-400 cm</t>
+          <t>300-350cm</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>£195.00</t>
+          <t>£170.00</t>
         </is>
       </c>
       <c r="H660" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I660" s="4" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -26047,148 +26051,148 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>50Ltr</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>300-350cm</t>
+          <t>350- 400cm</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>£170.00</t>
+          <t>£225.00</t>
         </is>
       </c>
       <c r="H661" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I661" s="4" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>QUERCUS acutissima</t>
+          <t>QUERCUS bicolor</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Sawtooth Oak</t>
+          <t>Swamp White Oak</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>50Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>350- 400cm</t>
-        </is>
-      </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>12/14</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr"/>
       <c r="G662" t="inlineStr">
         <is>
-          <t>£225.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H662" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I662" s="4" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>QUERCUS bicolor</t>
+          <t>QUERCUS buckleyi</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Swamp White Oak</t>
+          <t>Texas Red Oak</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>125-150cm</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
       <c r="G663" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H663" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I663" s="4" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>QUERCUS buckleyi</t>
+          <t>QUERCUS castaneifolia 'Green Spire'</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Texas Red Oak</t>
+          <t>Upright Chestnut-Leaved Oak</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>125-150cm</t>
-        </is>
-      </c>
-      <c r="F664" t="inlineStr"/>
+          <t>350-400 cm</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£190.00</t>
         </is>
       </c>
       <c r="H664" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I664" s="4" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -26203,63 +26207,59 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>350-400 cm</t>
+          <t>350-400cm</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>£190.00</t>
+          <t>£165.00</t>
         </is>
       </c>
       <c r="H665" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I665" s="4" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>QUERCUS castaneifolia 'Green Spire'</t>
+          <t>QUERCUS cerris</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Upright Chestnut-Leaved Oak</t>
+          <t>Turkey Oak</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F666" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>100-125cm</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr"/>
       <c r="G666" t="inlineStr">
         <is>
-          <t>£165.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H666" t="n">
@@ -26270,7 +26270,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -26285,29 +26285,33 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F667" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H667" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I667" s="4" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -26322,22 +26326,22 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>35L tr</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>250-300cm</t>
+          <t>400-500cm</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>12 /14</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>£95.00</t>
+          <t>£190.00</t>
         </is>
       </c>
       <c r="H668" t="n">
@@ -26348,7 +26352,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -26363,226 +26367,222 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>35L tr</t>
+          <t>50Ltr</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>400-500cm</t>
+          <t>450-500cm</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>12 /14</t>
+          <t>18/20</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>£190.00</t>
+          <t>£360.00</t>
         </is>
       </c>
       <c r="H669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I669" s="4" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>QUERCUS cerris</t>
+          <t>QUERCUS coccifera</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Turkey Oak</t>
+          <t>Kermes Oak</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>50Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>450-500cm</t>
-        </is>
-      </c>
-      <c r="F670" t="inlineStr">
-        <is>
-          <t>18/20</t>
-        </is>
-      </c>
+          <t>50-75cm</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr"/>
       <c r="G670" t="inlineStr">
         <is>
-          <t>£360.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H670" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I670" s="4" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>QUERCUS coccifera</t>
+          <t>QUERCUS coccinea</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Kermes Oak</t>
+          <t>Scarlet Oak</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>50-75cm</t>
-        </is>
-      </c>
-      <c r="F671" t="inlineStr"/>
+          <t>200-250cm</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£75.00</t>
         </is>
       </c>
       <c r="H671" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I671" s="4" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>QUERCUS coccinea</t>
+          <t>QUERCUS dentata</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Scarlet Oak</t>
+          <t>Japanese Emperor Oak</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>60-90cm</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr"/>
       <c r="G672" t="inlineStr">
         <is>
-          <t>£75.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H672" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I672" s="4" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>QUERCUS dentata</t>
+          <t>QUERCUS falcata 'Pagodifolia'</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Japanese Emperor Oak</t>
+          <t>Cherrybark Red Oak</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>60-90cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H673" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I673" s="4" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>QUERCUS falcata 'Pagodifolia'</t>
+          <t>QUERCUS ilex</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Cherrybark Red Oak</t>
+          <t>Holm Oak</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>150-200cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
       <c r="G674" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H674" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I674" s="4" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -26597,29 +26597,29 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H675" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I675" s="4" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -26634,70 +26634,70 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F676" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£215.00</t>
         </is>
       </c>
       <c r="H676" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I676" s="4" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>QUERCUS ilex</t>
+          <t>QUERCUS imbricaria</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Holm Oak</t>
+          <t>Shingle Oak</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F677" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>150-200cm</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr">
         <is>
-          <t>£215.00</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H677" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I677" s="4" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -26712,107 +26712,107 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F678" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H678" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I678" s="4" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>QUERCUS imbricaria</t>
+          <t>QUERCUS macrocarpa</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Shingle Oak</t>
+          <t>Bur Oak</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F679" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr"/>
       <c r="G679" t="inlineStr">
         <is>
-          <t>£95.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H679" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I679" s="4" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>QUERCUS macrocarpa</t>
+          <t>QUERCUS myrsinifolia</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Bur Oak</t>
+          <t>Chinese Evergreen Oak</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
       <c r="G680" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H680" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I680" s="4" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -26827,44 +26827,44 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>125-150cm</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
       <c r="G681" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£60.00</t>
         </is>
       </c>
       <c r="H681" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I681" s="4" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>QUERCUS myrsinifolia</t>
+          <t>QUERCUS nigra</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Chinese Evergreen Oak</t>
+          <t>Water Oak</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -26875,18 +26875,18 @@
       <c r="F682" t="inlineStr"/>
       <c r="G682" t="inlineStr">
         <is>
-          <t>£60.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H682" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I682" s="4" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -26901,29 +26901,29 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>125-150cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H683" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I683" s="4" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -26938,70 +26938,70 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>50Ltr</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F684" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£260.00</t>
         </is>
       </c>
       <c r="H684" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I684" s="4" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>QUERCUS nigra</t>
+          <t>QUERCUS palustris</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Water Oak</t>
+          <t>Pin Oak</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>50Ltr</t>
+          <t>1.5Ltr</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F685" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>75-100cm</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr">
         <is>
-          <t>£260.00</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="H685" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I685" s="4" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -27016,29 +27016,29 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>90 -120cm</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr">
         <is>
-          <t>£16.50</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="H686" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I686" s="4" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -27053,29 +27053,29 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>90 -120cm</t>
+          <t>140-160cm</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr">
         <is>
-          <t>£24.00</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H687" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="I687" s="4" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -27090,29 +27090,33 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F688" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>10/ 12</t>
+        </is>
+      </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£185.00</t>
         </is>
       </c>
       <c r="H688" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I688" s="4" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -27127,74 +27131,70 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>70Ltr</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>350-400cm</t>
+          <t>250-300cm</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>10/ 12</t>
+          <t>Specimen</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>£185.00</t>
+          <t>£295.00</t>
         </is>
       </c>
       <c r="H689" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I689" s="4" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>QUERCUS palustris</t>
+          <t>QUERCUS palustris 'Green Pillar'</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Pin Oak</t>
+          <t>Upright Pin Oak</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>70Ltr</t>
+          <t>7.5 Ltr</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F690" t="inlineStr">
-        <is>
-          <t>Specimen</t>
-        </is>
-      </c>
+          <t>150-175cm</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr"/>
       <c r="G690" t="inlineStr">
         <is>
-          <t>£295.00</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="H690" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I690" s="4" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -27209,29 +27209,29 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>7.5 Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>150-175cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
       <c r="G691" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H691" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I691" s="4" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -27246,18 +27246,22 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F692" t="inlineStr"/>
+          <t>200-250 cm</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H692" t="n">
@@ -27268,48 +27272,44 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>QUERCUS palustris 'Green Pillar'</t>
+          <t>QUERCUS petraea</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Upright Pin Oak</t>
+          <t>Sessile Oak</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr"/>
       <c r="G693" t="inlineStr">
         <is>
-          <t>£95.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H693" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="I693" s="4" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -27324,29 +27324,29 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
       <c r="G694" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H694" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I694" s="4" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -27361,18 +27361,22 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>B/R</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F695" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£105.00</t>
         </is>
       </c>
       <c r="H695" t="n">
@@ -27383,48 +27387,44 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>QUERCUS petraea</t>
+          <t>QUERCUS phellos</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Sessile Oak</t>
+          <t>Willow Oak</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>B/R</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>140-160cm</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr"/>
       <c r="G696" t="inlineStr">
         <is>
-          <t>£105.00</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H696" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I696" s="4" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -27439,70 +27439,70 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F697" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£115.00</t>
         </is>
       </c>
       <c r="H697" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I697" s="4" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>QUERCUS phellos</t>
+          <t>QUERCUS phillyreoides</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Willow Oak</t>
+          <t>Black Ridge Oak</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F698" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr"/>
       <c r="G698" t="inlineStr">
         <is>
-          <t>£115.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H698" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I698" s="4" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -27517,66 +27517,66 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>90-120cm.cm</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
       <c r="G699" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H699" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I699" s="4" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>QUERCUS phillyreoides</t>
+          <t>QUERCUS pubescens</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Black Ridge Oak</t>
+          <t>Downy Oak</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>90-120cm.cm</t>
+          <t>175-200cm</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
       <c r="G700" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H700" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I700" s="4" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -27591,29 +27591,33 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F701" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£180.00</t>
         </is>
       </c>
       <c r="H701" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I701" s="4" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -27628,63 +27632,59 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>70ltr</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>300-350cm</t>
+          <t>400-450cm</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>£180.00</t>
+          <t>£260.00</t>
         </is>
       </c>
       <c r="H702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I702" s="4" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>17453</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>QUERCUS pubescens</t>
+          <t>QUERCUS pyrenaica</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Downy Oak</t>
+          <t>Pyrenean Oak</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>70ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>400-450cm</t>
-        </is>
-      </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>12/14</t>
-        </is>
-      </c>
+          <t>150-175cm</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr">
         <is>
-          <t>£260.00</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H703" t="n">
@@ -27695,7 +27695,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -27710,70 +27710,70 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>150-175cm</t>
-        </is>
-      </c>
-      <c r="F704" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£215.00</t>
         </is>
       </c>
       <c r="H704" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I704" s="4" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>QUERCUS pyrenaica</t>
+          <t>QUERCUS robur</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Pyrenean Oak</t>
+          <t>English Oak</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>1 Ltr</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>100 -125cm</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr"/>
       <c r="G705" t="inlineStr">
         <is>
-          <t>£215.00</t>
+          <t>£12.00</t>
         </is>
       </c>
       <c r="H705" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I705" s="4" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -27788,29 +27788,29 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>1 Ltr</t>
+          <t>1Ltr</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>100 -125cm</t>
+          <t>75-100cm</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
       <c r="G706" t="inlineStr">
         <is>
-          <t>£12.00</t>
+          <t>£9.00</t>
         </is>
       </c>
       <c r="H706" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I706" s="4" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -27825,29 +27825,29 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>1Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
       <c r="G707" t="inlineStr">
         <is>
-          <t>£9.00</t>
+          <t>£22.50</t>
         </is>
       </c>
       <c r="H707" t="n">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="I707" s="4" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -27862,29 +27862,29 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
       <c r="G708" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H708" t="n">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="I708" s="4" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -27899,29 +27899,29 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>150-200cm</t>
+          <t>200-250 cm</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
       <c r="G709" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H709" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I709" s="4" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -27936,107 +27936,107 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>200-250 cm</t>
-        </is>
-      </c>
-      <c r="F710" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£160.00</t>
         </is>
       </c>
       <c r="H710" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I710" s="4" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>QUERCUS robur</t>
+          <t>QUERCUS robur 'Crimson Spire'</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>English Oak</t>
+          <t>Crimson Spire Oak</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F711" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>75-100cm</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr"/>
       <c r="G711" t="inlineStr">
         <is>
-          <t>£160.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H711" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I711" s="4" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>QUERCUS robur 'Crimson Spire'</t>
+          <t>QUERCUS robur 'Fastigiata Koster'</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Crimson Spire Oak</t>
+          <t>Koster Upright Oak</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>250- 300cm</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H712" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I712" s="4" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -28051,70 +28051,70 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>50Ltr</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>250- 300cm</t>
-        </is>
-      </c>
-      <c r="F713" t="inlineStr"/>
+          <t>400-450cm</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£215.00</t>
         </is>
       </c>
       <c r="H713" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I713" s="4" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>QUERCUS robur 'Fastigiata Koster'</t>
+          <t>QUERCUS rubra</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Koster Upright Oak</t>
+          <t>Red Oak</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>50Ltr</t>
+          <t>3 Ltr</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>400-450cm</t>
-        </is>
-      </c>
-      <c r="F714" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>125-150cm</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr">
         <is>
-          <t>£215.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H714" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="I714" s="4" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -28129,29 +28129,29 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>3 Ltr</t>
+          <t>5L tr</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>125-150cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H715" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="I715" s="4" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -28166,140 +28166,140 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>5L tr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>150-200cm</t>
+          <t>275-300cm</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H716" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I716" s="4" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>QUERCUS rubra</t>
+          <t>QUERCUS suber</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Red Oak</t>
+          <t>Cork Oak</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>275-300cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
       <c r="G717" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H717" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I717" s="4" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>QUERCUS suber</t>
+          <t>QUERCUS texana</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Cork Oak</t>
+          <t>Texan Oak</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>140-160cm</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
       <c r="G718" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H718" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I718" s="4" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>QUERCUS texana</t>
+          <t>QUERCUS turneri 'Pseudoturneri'</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Texan Oak</t>
+          <t>Turners Oak</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>140-160cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
       <c r="G719" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H719" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I719" s="4" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -28314,29 +28314,29 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>120-150cm</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
       <c r="G720" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H720" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I720" s="4" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -28351,107 +28351,107 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>50Ltr</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F721" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£295.00</t>
         </is>
       </c>
       <c r="H721" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I721" s="4" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>QUERCUS turneri 'Pseudoturneri'</t>
+          <t>QUERCUS virginiana</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Turners Oak</t>
+          <t>Southern Live Oak</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>50Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>75-100cm</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr"/>
       <c r="G722" t="inlineStr">
         <is>
-          <t>£295.00</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H722" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I722" s="4" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>QUERCUS virginiana</t>
+          <t>RHUS typhina</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Southern Live Oak</t>
+          <t>Stag's Horn Sumach</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>175-200cm</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
       <c r="G723" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H723" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I723" s="4" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -28466,29 +28466,29 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
       <c r="G724" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£60.00</t>
         </is>
       </c>
       <c r="H724" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I724" s="4" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -28503,66 +28503,66 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>130Ltr</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>200-250cm</t>
+          <t>350-400cm</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
       <c r="G725" t="inlineStr">
         <is>
-          <t>£60.00</t>
+          <t>£295.00</t>
         </is>
       </c>
       <c r="H725" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I725" s="4" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>RHUS typhina</t>
+          <t>RHUS typhina laciniata</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Stag's Horn Sumach</t>
+          <t>Cutleaf Staghorn Sumach</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>130Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>350-400cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
       <c r="G726" t="inlineStr">
         <is>
-          <t>£295.00</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H726" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I726" s="4" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -28577,75 +28577,79 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F727" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>14/16</t>
+        </is>
+      </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£225.00</t>
         </is>
       </c>
       <c r="H727" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I727" s="4" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>RHUS typhina laciniata</t>
+          <t>ROBINIA 'Casque Rouge'</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Cutleaf Staghorn Sumach</t>
+          <t>False Acacia</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>250-300cm</t>
+          <t>300- 400cm</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>£225.00</t>
+          <t>£195.00</t>
         </is>
       </c>
       <c r="H728" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I728" s="4" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>ROBINIA 'Casque Rouge'</t>
+          <t>ROBINIA pseudoacacia 'Frisia'</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -28655,33 +28659,29 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>300- 400cm</t>
-        </is>
-      </c>
-      <c r="F729" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>175-200cm</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr"/>
       <c r="G729" t="inlineStr">
         <is>
-          <t>£195.00</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H729" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I729" s="4" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -28696,103 +28696,103 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
       <c r="G730" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£60.00</t>
         </is>
       </c>
       <c r="H730" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I730" s="4" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>ROBINIA pseudoacacia 'Frisia'</t>
+          <t>SALIX alba 'Chermesina'</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>False Acacia</t>
+          <t>Scarlet Willow</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>200-250cm</t>
+          <t>175-200cm</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr">
         <is>
-          <t>£60.00</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H731" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I731" s="4" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>SALIX alba 'Chermesina'</t>
+          <t>SALIX alba 'Tristis'</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Scarlet Willow</t>
+          <t>Golden Weeping Willow</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
       <c r="G732" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H732" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I732" s="4" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -28807,59 +28807,59 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F733" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£85.00</t>
         </is>
       </c>
       <c r="H733" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I733" s="4" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>SALIX alba 'Tristis'</t>
+          <t>SALIX babylonica 'Tortuosa'</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Golden Weeping Willow</t>
+          <t>Dragon's Claw Willow</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F734" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>175-200cm</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr"/>
       <c r="G734" t="inlineStr">
         <is>
-          <t>£85.00</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H734" t="n">
@@ -28870,17 +28870,17 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>SALIX babylonica 'Tortuosa'</t>
+          <t>SALIX caprea 'Pendula'</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Dragon's Claw Willow</t>
+          <t>Kilmarnock Willow</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -28890,24 +28890,24 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>120-150cm</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
       <c r="G735" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H735" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I735" s="4" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -28922,39 +28922,39 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>120-150cm</t>
+          <t>125-150cm</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
       <c r="G736" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H736" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I736" s="4" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>SALIX caprea 'Pendula'</t>
+          <t>SALIX integra 'Hakuro-nishiki'</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Kilmarnock Willow</t>
+          <t>Japanese Dappled Willow [Half Standards]</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>125-150cm</t>
+          <t>175-200cm</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -28981,81 +28981,81 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>SALIX integra 'Hakuro-nishiki'</t>
+          <t>SAMBUCUS nigra</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Japanese Dappled Willow [Half Standards]</t>
+          <t>Elder</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
       <c r="G738" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H738" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I738" s="4" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>SAMBUCUS nigra</t>
+          <t>SCIADOPITYS verticillata</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Elder</t>
+          <t>Umbrella Pine</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>60-90cm</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
       <c r="G739" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="H739" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I739" s="4" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -29070,44 +29070,44 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>60-90cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
       <c r="G740" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H740" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I740" s="4" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>SCIADOPITYS verticillata</t>
+          <t>SEQUOIA sempervirens</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Umbrella Pine</t>
+          <t>Coastal Redwood</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -29118,18 +29118,18 @@
       <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H741" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I741" s="4" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -29144,76 +29144,76 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
       <c r="G742" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£90.00</t>
         </is>
       </c>
       <c r="H742" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I742" s="4" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>SEQUOIA sempervirens</t>
+          <t>SEQUOIADENDRON giganteum</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Coastal Redwood</t>
+          <t>Wellingtonia or Giant Redwood</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>200-250cm</t>
+          <t>50-75cm</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
       <c r="G743" t="inlineStr">
         <is>
-          <t>£90.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H743" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I743" s="4" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>SEQUOIADENDRON giganteum</t>
+          <t>SOPHORA japonica</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Wellingtonia or Giant Redwood</t>
+          <t>Japanese Pagoda</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -29223,66 +29223,66 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>50-75cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
       <c r="G744" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H744" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="I744" s="4" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>SOPHORA japonica</t>
+          <t>SORBUS  'Golden Wonder'</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Japanese Pagoda</t>
+          <t>Mountain Ash</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>200-225cm</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
       <c r="G745" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H745" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="I745" s="4" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>SORBUS  'Golden Wonder'</t>
+          <t>SORBUS 'Eastern Promise'</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -29292,29 +29292,29 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>200-225cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
       <c r="G746" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H746" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I746" s="4" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -29329,70 +29329,70 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F747" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£145.00</t>
         </is>
       </c>
       <c r="H747" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I747" s="4" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>SORBUS 'Eastern Promise'</t>
+          <t>SORBUS 'Olympic Flame'</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Mountain Ash</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F748" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>100-125cm</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr"/>
       <c r="G748" t="inlineStr">
         <is>
-          <t>£145.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H748" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I748" s="4" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -29407,55 +29407,55 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>175 -200cm</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
       <c r="G749" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H749" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I749" s="4" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>SORBUS 'Olympic Flame'</t>
+          <t>SORBUS aria 'Lutescens'</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Whitebeam</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>175 -200cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
       <c r="G750" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H750" t="n">
@@ -29466,12 +29466,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>SORBUS aria 'Lutescens'</t>
+          <t>SORBUS aria 'Magnifica'</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -29486,24 +29486,24 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>150-200cm</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
       <c r="G751" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H751" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I751" s="4" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -29518,70 +29518,70 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F752" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£175.00</t>
         </is>
       </c>
       <c r="H752" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I752" s="4" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>SORBUS aria 'Magnifica'</t>
+          <t>SORBUS aucuparia</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Whitebeam</t>
+          <t>Rowan or Mountain Ash</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F753" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>120-150cm</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
-          <t>£175.00</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="H753" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I753" s="4" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -29596,29 +29596,29 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>120-150cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
       <c r="G754" t="inlineStr">
         <is>
-          <t>£24.00</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H754" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I754" s="4" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29633,29 +29633,33 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F755" t="inlineStr"/>
+          <t>350-400 cm</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>12/ 14</t>
+        </is>
+      </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£185.00</t>
         </is>
       </c>
       <c r="H755" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I755" s="4" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -29670,22 +29674,22 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>35Lt r</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>350-400 cm</t>
+          <t>400-450cm.cm</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>12/ 14</t>
+          <t>14/16</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>£185.00</t>
+          <t>£225.00</t>
         </is>
       </c>
       <c r="H756" t="n">
@@ -29696,7 +29700,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -29711,84 +29715,80 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>35Lt r</t>
+          <t>35Ltr.</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>400-450cm.cm</t>
+          <t>350-400cm</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>10/ 12</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>£225.00</t>
+          <t>£155.00</t>
         </is>
       </c>
       <c r="H757" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I757" s="4" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>SORBUS aucuparia</t>
+          <t>SORBUS aucuparia 'Autumn Spire'</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Rowan or Mountain Ash</t>
+          <t>Upright Mountain Ash</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>35Ltr.</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>10/ 12</t>
-        </is>
-      </c>
+          <t>125-150cm</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr"/>
       <c r="G758" t="inlineStr">
         <is>
-          <t>£155.00</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H758" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I758" s="4" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>SORBUS aucuparia 'Autumn Spire'</t>
+          <t>Sorbus aucuparia 'Fastigiata'</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Upright Mountain Ash</t>
+          <t>Upright Rowan</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -29808,114 +29808,118 @@
         </is>
       </c>
       <c r="H759" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I759" s="4" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia 'Fastigiata'</t>
+          <t>SORBUS aucuparia 'Sheerwater Seedling'</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Upright Rowan</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>125-150cm</t>
+          <t>200-225cm</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H760" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I760" s="4" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>SORBUS aucuparia 'Sheerwater Seedling'</t>
+          <t>SORBUS commixta</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Japanese Rowan</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>200-225cm</t>
+          <t>140-160cm</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H761" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I761" s="4" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>SORBUS commixta</t>
+          <t>SORBUS hupehensis 'Pink Pagoda'</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Japanese Rowan</t>
+          <t>Mountain Ash</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>140-160cm</t>
-        </is>
-      </c>
-      <c r="F762" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£145.00</t>
         </is>
       </c>
       <c r="H762" t="n">
@@ -29926,48 +29930,44 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>SORBUS hupehensis 'Pink Pagoda'</t>
+          <t>SORBUS intermedia</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Mountain Ash</t>
+          <t>Swedish Whitebeam</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>350-400cm</t>
-        </is>
-      </c>
-      <c r="F763" t="inlineStr">
-        <is>
-          <t>10/12</t>
-        </is>
-      </c>
+          <t>150-200cm</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
-          <t>£145.00</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H763" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I763" s="4" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -29982,29 +29982,33 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>150-200cm</t>
-        </is>
-      </c>
-      <c r="F764" t="inlineStr"/>
+          <t>300-350cm</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£135.00</t>
         </is>
       </c>
       <c r="H764" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I764" s="4" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -30019,22 +30023,22 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>70Ltr</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>300-350cm</t>
+          <t>500-550cm</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>14/16</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>£135.00</t>
+          <t>£295.00</t>
         </is>
       </c>
       <c r="H765" t="n">
@@ -30045,122 +30049,118 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>SORBUS intermedia</t>
+          <t>SORBUS pseudovilmorinii</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Swedish Whitebeam</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>70Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>500-550cm</t>
-        </is>
-      </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>14/16</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr">
         <is>
-          <t>£295.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H766" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I766" s="4" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>SORBUS pseudovilmorinii</t>
+          <t>SORBUS thur. 'Fastigiata'</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Hybrid Whitebeam, Service Tree</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>200-225cm</t>
         </is>
       </c>
       <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H767" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I767" s="4" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>SORBUS thur. 'Fastigiata'</t>
+          <t>SORBUS torminalis</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Hybrid Whitebeam, Service Tree</t>
+          <t>Wild Service Tree</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>200-225cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H768" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I768" s="4" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -30175,59 +30175,63 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>90Ltr</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F769" t="inlineStr"/>
+          <t>450-500cm</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>18/20</t>
+        </is>
+      </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£345.00</t>
         </is>
       </c>
       <c r="H769" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="I769" s="4" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>SORBUS torminalis</t>
+          <t>SORBUS vilmorinii</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Wild Service Tree</t>
+          <t>Vilmorin's rowan</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>90Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>450-500cm</t>
+          <t>300-350cm</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>£345.00</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H770" t="n">
@@ -30238,58 +30242,54 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>SORBUS vilmorinii</t>
+          <t>STEWARTIA pseudocamellia</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Vilmorin's rowan</t>
+          <t>Japanese Stewartia</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F771" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr">
         <is>
-          <t>£95.00</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H771" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I771" s="4" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>STEWARTIA pseudocamellia</t>
+          <t>STYRAX japonicus</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Japanese Stewartia</t>
+          <t>Japanese Snowball</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -30299,98 +30299,98 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F772" t="inlineStr"/>
       <c r="G772" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H772" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I772" s="4" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>STYRAX japonicus</t>
+          <t>SYRINGA vulgaris 'Madame Lemoine'</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Japanese Snowball</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>75-100cm</t>
         </is>
       </c>
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H773" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I773" s="4" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>SYRINGA vulgaris 'Madame Lemoine'</t>
+          <t>TAXODIUM distichum</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Lilac</t>
+          <t>Swamp Cypress</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H774" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I774" s="4" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -30405,12 +30405,12 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -30420,14 +30420,14 @@
         </is>
       </c>
       <c r="H775" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I775" s="4" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -30442,66 +30442,66 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>150-175cm</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="H776" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I776" s="4" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>TAXODIUM distichum</t>
+          <t>TAXUS baccata</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Swamp Cypress</t>
+          <t>Yew</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>150-175cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£22.50</t>
         </is>
       </c>
       <c r="H777" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="I777" s="4" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -30516,76 +30516,76 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>7.5Ltr</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
       <c r="G778" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£45.00</t>
         </is>
       </c>
       <c r="H778" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="I778" s="4" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>TAXUS baccata</t>
+          <t>TAXUS baccata 'Fastigiata Robusta'</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Yew</t>
+          <t>English Yew</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>7.5Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>60-80cm</t>
         </is>
       </c>
       <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£22.50</t>
         </is>
       </c>
       <c r="H779" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I779" s="4" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>TAXUS baccata 'Fastigiata Robusta'</t>
+          <t>TAXUS baccata Fastigiata Aurea</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>English Yew</t>
+          <t>Golden Irish Yew</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -30595,34 +30595,34 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>60-80cm</t>
+          <t>50-75cm</t>
         </is>
       </c>
       <c r="F780" t="inlineStr"/>
       <c r="G780" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£24.00</t>
         </is>
       </c>
       <c r="H780" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I780" s="4" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>TAXUS baccata Fastigiata Aurea</t>
+          <t>TETRADIUM daniellii</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Golden Irish Yew</t>
+          <t>Bee-bee Tree</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -30632,24 +30632,24 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>50-75cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
-          <t>£24.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H781" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I781" s="4" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -30664,55 +30664,55 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H782" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I782" s="4" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>TETRADIUM daniellii</t>
+          <t>THUJA occidentalis 'Smaragd'</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Bee-bee Tree</t>
+          <t>White Cedar</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>200-250cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£22.50</t>
         </is>
       </c>
       <c r="H783" t="n">
@@ -30723,7 +30723,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -30738,71 +30738,71 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>180Ltr</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>90-120cm</t>
+          <t>300-325cm</t>
         </is>
       </c>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£280.00</t>
         </is>
       </c>
       <c r="H784" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I784" s="4" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>THUJA occidentalis 'Smaragd'</t>
+          <t>THUJA plicata 'Atrovirens'</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>White Cedar</t>
+          <t>Western Red Cedar</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>180Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>300-325cm</t>
+          <t>75-100cm</t>
         </is>
       </c>
       <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
-          <t>£280.00</t>
+          <t>£18.00</t>
         </is>
       </c>
       <c r="H785" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I785" s="4" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>THUJA plicata 'Atrovirens'</t>
+          <t>THUJA plicata 'Gelderland'</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -30817,7 +30817,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>60-90cm</t>
         </is>
       </c>
       <c r="F786" t="inlineStr"/>
@@ -30827,24 +30827,24 @@
         </is>
       </c>
       <c r="H786" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I786" s="4" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>THUJA plicata 'Gelderland'</t>
+          <t>THUJOPSIS dolabrata</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Western Red Cedar</t>
+          <t>Hiba Arborvitae</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -30854,102 +30854,102 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>60-90cm</t>
+          <t>30-50cm</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
-          <t>£18.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H787" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I787" s="4" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>THUJOPSIS dolabrata</t>
+          <t>TILIA americana 'American Sentry'</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Hiba Arborvitae</t>
+          <t>Sentry Linden</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>30-50cm</t>
-        </is>
-      </c>
-      <c r="F788" t="inlineStr"/>
+          <t>450-500cm</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£185.00</t>
         </is>
       </c>
       <c r="H788" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I788" s="4" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>TILIA americana 'American Sentry'</t>
+          <t>TILIA cordata</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Sentry Linden</t>
+          <t>Small-leaved Lime</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3 Ltr</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>450-500cm</t>
-        </is>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>12/14</t>
-        </is>
-      </c>
+          <t>125-150 cm</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr">
         <is>
-          <t>£185.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H789" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="I789" s="4" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -30964,29 +30964,33 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>3 Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>125-150 cm</t>
-        </is>
-      </c>
-      <c r="F790" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£80.00</t>
         </is>
       </c>
       <c r="H790" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="I790" s="4" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -31001,74 +31005,70 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>250-300cm</t>
+          <t>400-450cm</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>14/16</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>£80.00</t>
+          <t>£215.00</t>
         </is>
       </c>
       <c r="H791" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I791" s="4" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>TILIA cordata</t>
+          <t>TILIA cordata 'Greenspire '</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Small-leaved Lime</t>
+          <t>Small-Leaved Lime</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>5 Ltr</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>400-450cm</t>
-        </is>
-      </c>
-      <c r="F792" t="inlineStr">
-        <is>
-          <t>14/16</t>
-        </is>
-      </c>
+          <t>100-125cm</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr"/>
       <c r="G792" t="inlineStr">
         <is>
-          <t>£215.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H792" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I792" s="4" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -31083,66 +31083,66 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>5 Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>125-150cm</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="H793" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I793" s="4" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>TILIA cordata 'Greenspire '</t>
+          <t>TILIA cordata 'Winter Orange'</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Small-Leaved Lime</t>
+          <t>Small-leaved Lime</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>5 Ltr</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>125-150cm</t>
+          <t>175-200cm</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
       <c r="G794" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="H794" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I794" s="4" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -31157,29 +31157,29 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>5 Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>175-200cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F795" t="inlineStr"/>
       <c r="G795" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H795" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I795" s="4" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -31194,29 +31194,29 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>200-250cm</t>
         </is>
       </c>
       <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H796" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I796" s="4" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -31231,70 +31231,70 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>200-250cm</t>
-        </is>
-      </c>
-      <c r="F797" t="inlineStr"/>
+          <t>400-450cm</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£295.00</t>
         </is>
       </c>
       <c r="H797" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I797" s="4" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>TILIA cordata 'Winter Orange'</t>
+          <t>TILIA henryana</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Small-leaved Lime</t>
+          <t>Henry's Lime</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>400-450cm</t>
-        </is>
-      </c>
-      <c r="F798" t="inlineStr">
-        <is>
-          <t>16/18</t>
-        </is>
-      </c>
+          <t>90-120cm</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr"/>
       <c r="G798" t="inlineStr">
         <is>
-          <t>£295.00</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H798" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I798" s="4" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -31309,70 +31309,70 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F799" t="inlineStr"/>
+          <t>175-200cm</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£85.00</t>
         </is>
       </c>
       <c r="H799" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I799" s="4" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>TILIA henryana</t>
+          <t>TILIA platyphyllos</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Henry's Lime</t>
+          <t>Broad-leaved Lime</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>175-200cm</t>
-        </is>
-      </c>
-      <c r="F800" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
+          <t>120-150cm</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr"/>
       <c r="G800" t="inlineStr">
         <is>
-          <t>£85.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H800" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="I800" s="4" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -31387,39 +31387,43 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F801" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£75.00</t>
         </is>
       </c>
       <c r="H801" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I801" s="4" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>TILIA platyphyllos</t>
+          <t>TILIA x euchlora</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Broad-leaved Lime</t>
+          <t>European White Lime</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -31429,65 +31433,61 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F802" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>200-250cm</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr"/>
       <c r="G802" t="inlineStr">
         <is>
-          <t>£75.00</t>
+          <t>£55.00</t>
         </is>
       </c>
       <c r="H802" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I802" s="4" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>TILIA x euchlora</t>
+          <t>TILIA x europaea 'Pallida'</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>European White Lime</t>
+          <t>Kaiser Linden</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>5 Ltr</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>200-250cm</t>
+          <t>120-150cm</t>
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H803" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I803" s="4" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -31502,29 +31502,33 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>5 Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>120-150cm</t>
-        </is>
-      </c>
-      <c r="F804" t="inlineStr"/>
+          <t>400-450cm</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£185.00</t>
         </is>
       </c>
       <c r="H804" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I804" s="4" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -31534,68 +31538,68 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Kaiser Linden</t>
+          <t>Kaiser Linden [5/yr pleached]</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>230Ltr</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>400-450cm</t>
+          <t>1.8x2x2mcm</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>£185.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="H805" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I805" s="4" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>TILIA x europaea 'Pallida'</t>
+          <t>TILIA x mongolica 'Harvest Gold'</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Kaiser Linden [5/yr pleached]</t>
+          <t>Mongolian Lime</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>230Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>1.8x2x2mcm</t>
+          <t>250cm</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£110.00</t>
         </is>
       </c>
       <c r="H806" t="n">
@@ -31606,7 +31610,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -31621,33 +31625,33 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>35L tr</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>250cm</t>
+          <t>400-500cm</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>14/16</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>£110.00</t>
+          <t>£225.00</t>
         </is>
       </c>
       <c r="H807" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I807" s="4" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>17487</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -31662,33 +31666,33 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>35L tr</t>
+          <t>35Lt r</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>400-500cm</t>
+          <t>400-500 cm</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>16/18</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>£225.00</t>
+          <t>£260.00</t>
         </is>
       </c>
       <c r="H808" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I808" s="4" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -31703,53 +31707,53 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>35Lt r</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>400-500 cm</t>
+          <t>400-450cm</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>£260.00</t>
+          <t>£165.00</t>
         </is>
       </c>
       <c r="H809" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I809" s="4" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>TILIA x mongolica 'Harvest Gold'</t>
+          <t>TOONA sinensis</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mongolian Lime</t>
+          <t>Chinese Cedar</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>35 Ltr</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>400-450cm</t>
+          <t>300-350cm.cm</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
@@ -31759,18 +31763,18 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>£165.00</t>
+          <t>£160.00</t>
         </is>
       </c>
       <c r="H810" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I810" s="4" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -31785,74 +31789,70 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>35 Ltr</t>
+          <t>35Ltr</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>300-350cm.cm</t>
+          <t>300-350cm</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>£160.00</t>
+          <t>£140.00</t>
         </is>
       </c>
       <c r="H811" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I811" s="4" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>TOONA sinensis</t>
+          <t>TSUGA canadensis</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Chinese Cedar</t>
+          <t>Eastern Hemlock</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>35Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>300-350cm</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
-      </c>
+          <t>75-100cm</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr">
         <is>
-          <t>£140.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H812" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I812" s="4" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -31867,103 +31867,103 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>12Ltr</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>75-100cm</t>
+          <t>140-160cm</t>
         </is>
       </c>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£60.00</t>
         </is>
       </c>
       <c r="H813" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I813" s="4" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>TSUGA canadensis</t>
+          <t>TSUGA heterophylla</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Eastern Hemlock</t>
+          <t>Western Hemlock</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>12Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>140-160cm</t>
+          <t>60-90cm</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
       <c r="G814" t="inlineStr">
         <is>
-          <t>£60.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H814" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I814" s="4" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>TSUGA heterophylla</t>
+          <t>ULMUS 'Lutece'</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Western Hemlock</t>
+          <t>Naguen Elm</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>5Ltr</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>60-90cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£31.50</t>
         </is>
       </c>
       <c r="H815" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I815" s="4" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -31978,49 +31978,53 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>5Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>100-125cm</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr"/>
+          <t>350-400cm</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H816" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I816" s="4" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>ULMUS 'Lutece'</t>
+          <t>ULMUS 'Sapporo Autumn Gold'</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Naguen Elm</t>
+          <t>Elm</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>25Ltr</t>
+          <t>20 Ltr</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>350-400cm</t>
+          <t>300-350cm</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
@@ -32034,138 +32038,134 @@
         </is>
       </c>
       <c r="H817" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I817" s="4" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>ULMUS 'Sapporo Autumn Gold'</t>
+          <t>ULMUS glabra 'Camperdownii'</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Elm</t>
+          <t>Camperdown Elm</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>20 Ltr</t>
+          <t>210Ltr</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>300-350cm</t>
+          <t>250-300cm</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>30/35</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>£95.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="H818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I818" s="4" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ULMUS glabra 'Camperdownii'</t>
+          <t>ULMUS hollandica ‘Wredei’</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Camperdown Elm</t>
+          <t>Golden Elm</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>210Ltr</t>
+          <t>20Ltr</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F819" t="inlineStr">
-        <is>
-          <t>30/35</t>
-        </is>
-      </c>
+          <t>150-200cm</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr"/>
       <c r="G819" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£65.00</t>
         </is>
       </c>
       <c r="H819" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I819" s="4" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ULMUS hollandica ‘Wredei’</t>
+          <t>ZELKOVA serrata</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Golden Elm</t>
+          <t>Japanese Zelkova</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>20Ltr</t>
+          <t>3Ltr</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>150-200cm</t>
+          <t>100-125cm</t>
         </is>
       </c>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="inlineStr">
         <is>
-          <t>£65.00</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="H820" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I820" s="4" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ZELKOVA serrata</t>
+          <t>ZELKOVA serrata 'Green Vase'</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -32180,24 +32180,24 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>100-125cm</t>
+          <t>90-120cm</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
       <c r="G821" t="inlineStr">
         <is>
-          <t>£25.50</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="H821" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I821" s="4" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -32212,65 +32212,28 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>3Ltr</t>
+          <t>25Ltr</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>90-120cm</t>
-        </is>
-      </c>
-      <c r="F822" t="inlineStr"/>
+          <t>250-300cm</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£95.00</t>
         </is>
       </c>
       <c r="H822" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I822" s="4" t="inlineStr"/>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>11168</t>
-        </is>
-      </c>
-      <c r="B823" t="inlineStr">
-        <is>
-          <t>ZELKOVA serrata 'Green Vase'</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>Japanese Zelkova</t>
-        </is>
-      </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>25Ltr</t>
-        </is>
-      </c>
-      <c r="E823" t="inlineStr">
-        <is>
-          <t>250-300cm</t>
-        </is>
-      </c>
-      <c r="F823" t="inlineStr">
-        <is>
-          <t>6/8</t>
-        </is>
-      </c>
-      <c r="G823" t="inlineStr">
-        <is>
-          <t>£95.00</t>
-        </is>
-      </c>
-      <c r="H823" t="n">
-        <v>4</v>
-      </c>
-      <c r="I823" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
